--- a/Team-Data/2013-14/12-7-2013-14.xlsx
+++ b/Team-Data/2013-14/12-7-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -754,22 +821,22 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM2" t="n">
         <v>12</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
         <v>24</v>
@@ -787,13 +854,13 @@
         <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -802,16 +869,16 @@
         <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -936,22 +1003,22 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
@@ -966,7 +1033,7 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>23</v>
@@ -990,13 +1057,13 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB3" t="n">
         <v>25</v>
       </c>
-      <c r="BB3" t="n">
-        <v>24</v>
-      </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>0.263</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,10 +1110,10 @@
         <v>34.2</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L4" t="n">
         <v>6.3</v>
@@ -1055,13 +1122,13 @@
         <v>18.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O4" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P4" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.75</v>
@@ -1076,16 +1143,16 @@
         <v>41.2</v>
       </c>
       <c r="U4" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
         <v>4.4</v>
@@ -1094,52 +1161,52 @@
         <v>22.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG4" t="n">
         <v>27</v>
       </c>
-      <c r="AG4" t="n">
-        <v>26</v>
-      </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>24</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
         <v>5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
       </c>
       <c r="AQ4" t="n">
         <v>16</v>
@@ -1157,28 +1224,28 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>23</v>
@@ -1330,10 +1397,10 @@
         <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>28</v>
@@ -1345,13 +1412,13 @@
         <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.444</v>
+        <v>0.471</v>
       </c>
       <c r="H6" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I6" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="J6" t="n">
-        <v>82.3</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.437</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.336</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S6" t="n">
         <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
         <v>3</v>
@@ -1485,10 +1552,10 @@
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1497,19 +1564,19 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
         <v>12</v>
       </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1524,7 +1591,7 @@
         <v>24</v>
       </c>
       <c r="AW6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
         <v>27</v>
@@ -1533,16 +1600,16 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1571,55 +1638,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.35</v>
+        <v>0.316</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="J7" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.415</v>
+        <v>0.417</v>
       </c>
       <c r="L7" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="P7" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0.744</v>
       </c>
       <c r="R7" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.3</v>
       </c>
       <c r="T7" t="n">
-        <v>44</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
         <v>18.4</v>
@@ -1628,46 +1695,46 @@
         <v>16.1</v>
       </c>
       <c r="W7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
         <v>4.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>92.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-7.3</v>
+        <v>-7.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>7</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>8</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1679,25 +1746,25 @@
         <v>22</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>27</v>
@@ -1706,25 +1773,25 @@
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
       </c>
       <c r="AY7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
         <v>27</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1753,124 +1820,124 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.619</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.464</v>
+        <v>0.461</v>
       </c>
       <c r="L8" t="n">
         <v>8.9</v>
       </c>
       <c r="M8" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="P8" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z8" t="n">
         <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.7</v>
+        <v>103.5</v>
       </c>
       <c r="AC8" t="n">
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
@@ -1879,19 +1946,19 @@
         <v>19</v>
       </c>
       <c r="AT8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1900,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -1935,55 +2002,55 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.718</v>
+        <v>0.714</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T9" t="n">
-        <v>46.1</v>
+        <v>45.7</v>
       </c>
       <c r="U9" t="n">
         <v>21.9</v>
@@ -1992,7 +2059,7 @@
         <v>14.3</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
         <v>5.8</v>
@@ -2001,25 +2068,25 @@
         <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AB9" t="n">
         <v>104</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>9</v>
       </c>
       <c r="AF9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9" t="n">
         <v>9</v>
@@ -2040,52 +2107,52 @@
         <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
         <v>10</v>
       </c>
       <c r="AO9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP9" t="n">
         <v>8</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
       </c>
       <c r="AY9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>23</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>22</v>
       </c>
       <c r="BA9" t="n">
         <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -2117,121 +2184,121 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J10" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>19.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.302</v>
       </c>
       <c r="O10" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.675</v>
+        <v>0.671</v>
       </c>
       <c r="R10" t="n">
         <v>14.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
         <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK10" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>15</v>
-      </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
         <v>21</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -2249,13 +2316,13 @@
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
@@ -2264,14 +2331,14 @@
         <v>11</v>
       </c>
       <c r="BA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC10" t="n">
         <v>16</v>
       </c>
-      <c r="BB10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>14</v>
-      </c>
       <c r="BD10" t="n">
         <v>10</v>
       </c>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.571</v>
+        <v>0.55</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.469</v>
+        <v>0.468</v>
       </c>
       <c r="L11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M11" t="n">
+        <v>23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="U11" t="n">
         <v>22.8</v>
       </c>
-      <c r="N11" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="O11" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="S11" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>22.9</v>
-      </c>
       <c r="V11" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>102.6</v>
+        <v>102.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2389,19 +2456,19 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
@@ -2410,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2425,34 +2492,34 @@
         <v>6</v>
       </c>
       <c r="AT11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>13</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>26</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>6.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2634,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>0.895</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J13" t="n">
-        <v>80</v>
+        <v>80.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.45</v>
       </c>
       <c r="L13" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
         <v>20.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.365</v>
+        <v>0.359</v>
       </c>
       <c r="O13" t="n">
-        <v>18.4</v>
+        <v>17.9</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.788</v>
+        <v>0.779</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="U13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>15.8</v>
@@ -2723,25 +2790,25 @@
         <v>7.3</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA13" t="n">
         <v>22.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>10.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,64 +2820,64 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>23</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
       </c>
       <c r="AN13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP13" t="n">
         <v>14</v>
       </c>
-      <c r="AO13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -2845,115 +2912,115 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>0.619</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M14" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.336</v>
+        <v>0.346</v>
       </c>
       <c r="O14" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="R14" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T14" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U14" t="n">
         <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
         <v>8.1</v>
       </c>
       <c r="X14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
@@ -2968,22 +3035,22 @@
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
         <v>3</v>
@@ -2998,7 +3065,7 @@
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>13</v>
@@ -3147,28 +3214,28 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
         <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX15" t="n">
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -3209,106 +3276,106 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0.474</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="J16" t="n">
-        <v>80.5</v>
+        <v>80.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.316</v>
+        <v>0.321</v>
       </c>
       <c r="O16" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P16" t="n">
         <v>20.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R16" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="T16" t="n">
         <v>40.9</v>
       </c>
       <c r="U16" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="V16" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W16" t="n">
         <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
         <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="AA16" t="n">
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-3.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,28 +3384,28 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
         <v>25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>5</v>
@@ -3353,7 +3420,7 @@
         <v>18</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>20</v>
@@ -3362,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -3391,88 +3458,88 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.737</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="J17" t="n">
-        <v>75.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.506</v>
+        <v>0.503</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.395</v>
+        <v>0.403</v>
       </c>
       <c r="O17" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="P17" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.762</v>
       </c>
       <c r="R17" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="U17" t="n">
         <v>23.8</v>
       </c>
       <c r="V17" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AB17" t="n">
         <v>103.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>5</v>
@@ -3484,7 +3551,7 @@
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,16 +3560,16 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,25 +3590,25 @@
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.211</v>
       </c>
       <c r="H18" t="n">
         <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.7</v>
+        <v>82.2</v>
       </c>
       <c r="K18" t="n">
         <v>0.419</v>
@@ -3600,61 +3667,61 @@
         <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O18" t="n">
         <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="R18" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S18" t="n">
         <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="U18" t="n">
         <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W18" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="X18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y18" t="n">
         <v>5.2</v>
       </c>
-      <c r="Y18" t="n">
-        <v>5.3</v>
-      </c>
       <c r="Z18" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>90.8</v>
+        <v>91.3</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>29</v>
@@ -3663,13 +3730,13 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3690,10 +3757,10 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -3702,13 +3769,13 @@
         <v>29</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -3755,121 +3822,121 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
+        <v>0.474</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.8</v>
+        <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="O19" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8</v>
+        <v>0.805</v>
       </c>
       <c r="R19" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="S19" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
         <v>45.4</v>
       </c>
       <c r="U19" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="W19" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>104.7</v>
+        <v>105.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF19" t="n">
         <v>15</v>
       </c>
-      <c r="AF19" t="n">
-        <v>19</v>
-      </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM19" t="n">
         <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
         <v>4</v>
@@ -3878,22 +3945,22 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY19" t="n">
         <v>27</v>
@@ -3902,13 +3969,13 @@
         <v>2</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF20" t="n">
         <v>15</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
@@ -4045,13 +4112,13 @@
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4060,10 +4127,10 @@
         <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>12</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4081,16 +4148,16 @@
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
         <v>17</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4197,28 +4264,28 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
         <v>26</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4236,13 +4303,13 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT21" t="n">
         <v>28</v>
@@ -4254,19 +4321,19 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>30</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4379,13 +4446,13 @@
         <v>4.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG22" t="n">
         <v>4</v>
@@ -4394,22 +4461,22 @@
         <v>10</v>
       </c>
       <c r="AI22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK22" t="n">
         <v>12</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>11</v>
-      </c>
       <c r="AL22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM22" t="n">
         <v>23</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4436,7 +4503,7 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>4</v>
@@ -4448,13 +4515,13 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4561,16 +4628,16 @@
         <v>-4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
         <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>5</v>
@@ -4579,25 +4646,25 @@
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>15</v>
       </c>
       <c r="AM23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN23" t="n">
         <v>12</v>
       </c>
       <c r="AO23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP23" t="n">
         <v>23</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>22</v>
       </c>
       <c r="AQ23" t="n">
         <v>15</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
@@ -4615,22 +4682,22 @@
         <v>18</v>
       </c>
       <c r="AV23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
         <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4665,94 +4732,94 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="H24" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="I24" t="n">
         <v>39.8</v>
       </c>
       <c r="J24" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="M24" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="O24" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="P24" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.698</v>
+        <v>0.699</v>
       </c>
       <c r="R24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S24" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="T24" t="n">
-        <v>46</v>
+        <v>46.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="W24" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>102.9</v>
+        <v>103.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.3</v>
+        <v>-7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>22</v>
       </c>
       <c r="AF24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
@@ -4767,34 +4834,34 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN24" t="n">
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
         <v>29</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
         <v>4</v>
       </c>
-      <c r="AT24" t="n">
-        <v>5</v>
-      </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>29</v>
@@ -4803,22 +4870,22 @@
         <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
         <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -4925,28 +4992,28 @@
         <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -4961,7 +5028,7 @@
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ25" t="n">
         <v>21</v>
@@ -4973,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>26</v>
@@ -4982,16 +5049,16 @@
         <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="H26" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J26" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>0.418</v>
+        <v>0.426</v>
       </c>
       <c r="O26" t="n">
         <v>18.2</v>
@@ -5068,16 +5135,16 @@
         <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S26" t="n">
         <v>32.5</v>
       </c>
       <c r="T26" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U26" t="n">
         <v>22.9</v>
@@ -5086,31 +5153,31 @@
         <v>14.4</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
         <v>3.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
         <v>21.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.2</v>
+        <v>106.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
         <v>4</v>
@@ -5134,55 +5201,55 @@
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
         <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS26" t="n">
         <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -5211,121 +5278,121 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>0.278</v>
+        <v>0.235</v>
       </c>
       <c r="H27" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>84.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L27" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.34</v>
       </c>
       <c r="O27" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="R27" t="n">
         <v>11.4</v>
       </c>
       <c r="S27" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="T27" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="U27" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V27" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="W27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM27" t="n">
         <v>13</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -5334,22 +5401,22 @@
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
         <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY27" t="n">
         <v>26</v>
@@ -5358,13 +5425,13 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.789</v>
+        <v>0.833</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
@@ -5411,67 +5478,67 @@
         <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.488</v>
+        <v>0.491</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="P28" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>34.5</v>
       </c>
       <c r="T28" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.8</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,19 +5556,19 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>17</v>
@@ -5525,16 +5592,16 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>21</v>
@@ -5668,49 +5735,49 @@
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR29" t="n">
         <v>4</v>
       </c>
-      <c r="AP29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>6</v>
-      </c>
       <c r="AS29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
         <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5719,13 +5786,13 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
         <v>3</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -5757,55 +5824,55 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.182</v>
+        <v>0.19</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M30" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.329</v>
+        <v>0.324</v>
       </c>
       <c r="O30" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P30" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="T30" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="U30" t="n">
         <v>19.3</v>
@@ -5814,22 +5881,22 @@
         <v>16.8</v>
       </c>
       <c r="W30" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="AC30" t="n">
         <v>-10</v>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
@@ -5847,7 +5914,7 @@
         <v>30</v>
       </c>
       <c r="AH30" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>27</v>
@@ -5856,7 +5923,7 @@
         <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>27</v>
@@ -5865,13 +5932,13 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="n">
         <v>17</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>16</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
@@ -5883,7 +5950,7 @@
         <v>30</v>
       </c>
       <c r="AT30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5901,10 +5968,10 @@
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF31" t="n">
         <v>15</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>13</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
@@ -6044,13 +6111,13 @@
         <v>7</v>
       </c>
       <c r="AM31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6059,7 +6126,7 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6071,13 +6138,13 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-7-2013-14</t>
+          <t>2013-12-07</t>
         </is>
       </c>
     </row>
